--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,6 +2374,3034 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120308060</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>701526</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6360046</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120308067</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>701574</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6360140</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120308071</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>701636</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6360182</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120308048</v>
+      </c>
+      <c r="B19" t="n">
+        <v>108548</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1489</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Alvarstånds</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>701438</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6359991</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120308107</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>701452</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6360109</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120308053</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>701497</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6359955</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120308106</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>701480</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6360120</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120308078</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103429</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>701622</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6360225</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120308080</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>701606</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6360224</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120308042</v>
+      </c>
+      <c r="B25" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>701451</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6359994</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120308109</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>701431</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6360091</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120308094</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97882</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>701557</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6360196</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120308100</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>701541</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6360151</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120308059</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>701524</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6359992</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120308317</v>
+      </c>
+      <c r="B30" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>701518</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6360129</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120308055</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>701519</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6359965</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120308086</v>
+      </c>
+      <c r="B32" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>701557</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6360196</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120308105</v>
+      </c>
+      <c r="B33" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>701480</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6360120</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120308112</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>701407</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6360080</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120308092</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>701557</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6360196</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120308068</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>701594</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6360147</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120308062</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>701524</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6360079</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120308102</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>701532</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6360143</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120308063</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>701532</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6360141</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120308066</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>701560</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6360140</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120308052</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>701467</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6359951</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120308043</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>701451</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6359994</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120308110</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106190</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>701423</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6360088</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308060</v>
+        <v>120308078</v>
       </c>
       <c r="B16" t="n">
-        <v>106190</v>
+        <v>103452</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,21 +2392,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701526</v>
+        <v>701622</v>
       </c>
       <c r="R16" t="n">
-        <v>6360046</v>
+        <v>6360225</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308067</v>
+        <v>120308052</v>
       </c>
       <c r="B17" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701574</v>
+        <v>701467</v>
       </c>
       <c r="R17" t="n">
-        <v>6360140</v>
+        <v>6359951</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308071</v>
+        <v>120308062</v>
       </c>
       <c r="B18" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701636</v>
+        <v>701524</v>
       </c>
       <c r="R18" t="n">
-        <v>6360182</v>
+        <v>6360079</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2697,10 +2697,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308048</v>
+        <v>120308059</v>
       </c>
       <c r="B19" t="n">
-        <v>108548</v>
+        <v>106214</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,55 +2709,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701438</v>
+        <v>701524</v>
       </c>
       <c r="R19" t="n">
-        <v>6359991</v>
+        <v>6359992</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,7 +2786,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2818,10 +2804,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308107</v>
+        <v>120308042</v>
       </c>
       <c r="B20" t="n">
-        <v>106190</v>
+        <v>108811</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2834,16 +2820,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2858,13 +2844,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701452</v>
+        <v>701451</v>
       </c>
       <c r="R20" t="n">
-        <v>6360109</v>
+        <v>6359994</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2907,7 +2893,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2925,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308053</v>
+        <v>120308105</v>
       </c>
       <c r="B21" t="n">
-        <v>106190</v>
+        <v>108811</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,16 +2927,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2958,20 +2944,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701497</v>
+        <v>701480</v>
       </c>
       <c r="R21" t="n">
-        <v>6359955</v>
+        <v>6360120</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3014,7 +3009,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3032,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308106</v>
+        <v>120308048</v>
       </c>
       <c r="B22" t="n">
-        <v>106190</v>
+        <v>108572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,41 +3039,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701480</v>
+        <v>701438</v>
       </c>
       <c r="R22" t="n">
-        <v>6360120</v>
+        <v>6359991</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,7 +3130,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3139,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308078</v>
+        <v>120308317</v>
       </c>
       <c r="B23" t="n">
-        <v>103429</v>
+        <v>94704</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3151,25 +3160,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220164</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3179,13 +3188,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701622</v>
+        <v>701518</v>
       </c>
       <c r="R23" t="n">
-        <v>6360225</v>
+        <v>6360129</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3225,11 +3234,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3249,7 +3253,7 @@
         <v>120308080</v>
       </c>
       <c r="B24" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3353,10 +3357,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308042</v>
+        <v>120308092</v>
       </c>
       <c r="B25" t="n">
-        <v>108787</v>
+        <v>106214</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3369,16 +3373,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3393,10 +3397,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701451</v>
+        <v>701557</v>
       </c>
       <c r="R25" t="n">
-        <v>6359994</v>
+        <v>6360196</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3442,7 +3446,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3460,10 +3464,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308109</v>
+        <v>120308106</v>
       </c>
       <c r="B26" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3500,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701431</v>
+        <v>701480</v>
       </c>
       <c r="R26" t="n">
-        <v>6360091</v>
+        <v>6360120</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3567,10 +3571,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308094</v>
+        <v>120308107</v>
       </c>
       <c r="B27" t="n">
-        <v>97882</v>
+        <v>106214</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3579,50 +3583,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701557</v>
+        <v>701452</v>
       </c>
       <c r="R27" t="n">
-        <v>6360196</v>
+        <v>6360109</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3683,10 +3678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308100</v>
+        <v>120308109</v>
       </c>
       <c r="B28" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,13 +3718,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701541</v>
+        <v>701431</v>
       </c>
       <c r="R28" t="n">
-        <v>6360151</v>
+        <v>6360091</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3790,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308059</v>
+        <v>120308068</v>
       </c>
       <c r="B29" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3830,13 +3825,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701524</v>
+        <v>701594</v>
       </c>
       <c r="R29" t="n">
-        <v>6359992</v>
+        <v>6360147</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3879,7 +3874,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3897,10 +3892,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308317</v>
+        <v>120308053</v>
       </c>
       <c r="B30" t="n">
-        <v>94681</v>
+        <v>106214</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3909,25 +3904,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3937,13 +3932,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701518</v>
+        <v>701497</v>
       </c>
       <c r="R30" t="n">
-        <v>6360129</v>
+        <v>6359955</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3983,6 +3978,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3999,10 +3999,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308055</v>
+        <v>120308066</v>
       </c>
       <c r="B31" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701519</v>
+        <v>701560</v>
       </c>
       <c r="R31" t="n">
-        <v>6359965</v>
+        <v>6360140</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4077,6 +4077,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4088,7 +4093,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4106,10 +4111,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308086</v>
+        <v>120308055</v>
       </c>
       <c r="B32" t="n">
-        <v>108787</v>
+        <v>106214</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4122,16 +4127,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4146,13 +4151,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701557</v>
+        <v>701519</v>
       </c>
       <c r="R32" t="n">
-        <v>6360196</v>
+        <v>6359965</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4195,7 +4200,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4213,10 +4218,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308105</v>
+        <v>120308071</v>
       </c>
       <c r="B33" t="n">
-        <v>108787</v>
+        <v>106214</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4229,16 +4234,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4246,29 +4251,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701480</v>
+        <v>701636</v>
       </c>
       <c r="R33" t="n">
-        <v>6360120</v>
+        <v>6360182</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4311,7 +4307,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4329,10 +4325,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308112</v>
+        <v>120308110</v>
       </c>
       <c r="B34" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4369,13 +4365,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701407</v>
+        <v>701423</v>
       </c>
       <c r="R34" t="n">
-        <v>6360080</v>
+        <v>6360088</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,10 +4432,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308092</v>
+        <v>120308112</v>
       </c>
       <c r="B35" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4476,10 +4472,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701557</v>
+        <v>701407</v>
       </c>
       <c r="R35" t="n">
-        <v>6360196</v>
+        <v>6360080</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4543,10 +4539,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308068</v>
+        <v>120308067</v>
       </c>
       <c r="B36" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4583,13 +4579,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701594</v>
+        <v>701574</v>
       </c>
       <c r="R36" t="n">
-        <v>6360147</v>
+        <v>6360140</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4650,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308062</v>
+        <v>120308086</v>
       </c>
       <c r="B37" t="n">
-        <v>106190</v>
+        <v>108811</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4666,16 +4662,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4690,13 +4686,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701524</v>
+        <v>701557</v>
       </c>
       <c r="R37" t="n">
-        <v>6360079</v>
+        <v>6360196</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4739,7 +4735,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4757,10 +4753,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308102</v>
+        <v>120308060</v>
       </c>
       <c r="B38" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4797,13 +4793,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701532</v>
+        <v>701526</v>
       </c>
       <c r="R38" t="n">
-        <v>6360143</v>
+        <v>6360046</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4846,7 +4842,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4864,10 +4860,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308063</v>
+        <v>120308102</v>
       </c>
       <c r="B39" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4907,10 +4903,10 @@
         <v>701532</v>
       </c>
       <c r="R39" t="n">
-        <v>6360141</v>
+        <v>6360143</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4953,7 +4949,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4971,10 +4967,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308066</v>
+        <v>120308043</v>
       </c>
       <c r="B40" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5011,10 +5007,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701560</v>
+        <v>701451</v>
       </c>
       <c r="R40" t="n">
-        <v>6360140</v>
+        <v>6359994</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5049,11 +5045,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5065,7 +5056,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5083,10 +5074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308052</v>
+        <v>120308100</v>
       </c>
       <c r="B41" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5123,13 +5114,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701467</v>
+        <v>701541</v>
       </c>
       <c r="R41" t="n">
-        <v>6359951</v>
+        <v>6360151</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5172,7 +5163,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5190,10 +5181,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308043</v>
+        <v>120308063</v>
       </c>
       <c r="B42" t="n">
-        <v>106190</v>
+        <v>106214</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5230,10 +5221,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701451</v>
+        <v>701532</v>
       </c>
       <c r="R42" t="n">
-        <v>6359994</v>
+        <v>6360141</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5297,10 +5288,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308110</v>
+        <v>120308094</v>
       </c>
       <c r="B43" t="n">
-        <v>106190</v>
+        <v>97905</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5309,41 +5300,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701423</v>
+        <v>701557</v>
       </c>
       <c r="R43" t="n">
-        <v>6360088</v>
+        <v>6360196</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2697,10 +2697,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308059</v>
+        <v>120308048</v>
       </c>
       <c r="B19" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,41 +2709,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701524</v>
+        <v>701438</v>
       </c>
       <c r="R19" t="n">
-        <v>6359992</v>
+        <v>6359991</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2786,7 +2800,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2804,10 +2818,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308042</v>
+        <v>120308059</v>
       </c>
       <c r="B20" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2820,16 +2834,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2844,10 +2858,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701451</v>
+        <v>701524</v>
       </c>
       <c r="R20" t="n">
-        <v>6359994</v>
+        <v>6359992</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2893,7 +2907,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2911,7 +2925,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308105</v>
+        <v>120308042</v>
       </c>
       <c r="B21" t="n">
         <v>108811</v>
@@ -2944,29 +2958,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701480</v>
+        <v>701451</v>
       </c>
       <c r="R21" t="n">
-        <v>6360120</v>
+        <v>6359994</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3009,7 +3014,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3027,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308048</v>
+        <v>120308105</v>
       </c>
       <c r="B22" t="n">
-        <v>108572</v>
+        <v>108811</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,30 +3044,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1489</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3070,24 +3075,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701438</v>
+        <v>701480</v>
       </c>
       <c r="R22" t="n">
-        <v>6359991</v>
+        <v>6360120</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308078</v>
+        <v>120308055</v>
       </c>
       <c r="B16" t="n">
-        <v>103452</v>
+        <v>106214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,21 +2392,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701622</v>
+        <v>701519</v>
       </c>
       <c r="R16" t="n">
-        <v>6360225</v>
+        <v>6359965</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2483,7 +2483,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308052</v>
+        <v>120308062</v>
       </c>
       <c r="B17" t="n">
         <v>106214</v>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701467</v>
+        <v>701524</v>
       </c>
       <c r="R17" t="n">
-        <v>6359951</v>
+        <v>6360079</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308062</v>
+        <v>120308048</v>
       </c>
       <c r="B18" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,41 +2602,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701524</v>
+        <v>701438</v>
       </c>
       <c r="R18" t="n">
-        <v>6360079</v>
+        <v>6359991</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2697,10 +2711,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308048</v>
+        <v>120308107</v>
       </c>
       <c r="B19" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,55 +2723,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701438</v>
+        <v>701452</v>
       </c>
       <c r="R19" t="n">
-        <v>6359991</v>
+        <v>6360109</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308059</v>
+        <v>120308060</v>
       </c>
       <c r="B20" t="n">
         <v>106214</v>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701524</v>
+        <v>701526</v>
       </c>
       <c r="R20" t="n">
-        <v>6359992</v>
+        <v>6360046</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308042</v>
+        <v>120308053</v>
       </c>
       <c r="B21" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,16 +2941,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701451</v>
+        <v>701497</v>
       </c>
       <c r="R21" t="n">
-        <v>6359994</v>
+        <v>6359955</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308105</v>
+        <v>120308043</v>
       </c>
       <c r="B22" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3065,29 +3065,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701480</v>
+        <v>701451</v>
       </c>
       <c r="R22" t="n">
-        <v>6360120</v>
+        <v>6359994</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3130,7 +3121,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3148,10 +3139,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308317</v>
+        <v>120308102</v>
       </c>
       <c r="B23" t="n">
-        <v>94704</v>
+        <v>106214</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,25 +3151,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3188,13 +3179,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701518</v>
+        <v>701532</v>
       </c>
       <c r="R23" t="n">
-        <v>6360129</v>
+        <v>6360143</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3234,6 +3225,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3250,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308080</v>
+        <v>120308059</v>
       </c>
       <c r="B24" t="n">
         <v>106214</v>
@@ -3290,10 +3286,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701606</v>
+        <v>701524</v>
       </c>
       <c r="R24" t="n">
-        <v>6360224</v>
+        <v>6359992</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3339,7 +3335,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3357,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308092</v>
+        <v>120308052</v>
       </c>
       <c r="B25" t="n">
         <v>106214</v>
@@ -3397,10 +3393,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701557</v>
+        <v>701467</v>
       </c>
       <c r="R25" t="n">
-        <v>6360196</v>
+        <v>6359951</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3446,7 +3442,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3464,7 +3460,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308106</v>
+        <v>120308112</v>
       </c>
       <c r="B26" t="n">
         <v>106214</v>
@@ -3504,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701480</v>
+        <v>701407</v>
       </c>
       <c r="R26" t="n">
-        <v>6360120</v>
+        <v>6360080</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3571,7 +3567,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308107</v>
+        <v>120308092</v>
       </c>
       <c r="B27" t="n">
         <v>106214</v>
@@ -3611,13 +3607,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701452</v>
+        <v>701557</v>
       </c>
       <c r="R27" t="n">
-        <v>6360109</v>
+        <v>6360196</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3678,7 +3674,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308109</v>
+        <v>120308100</v>
       </c>
       <c r="B28" t="n">
         <v>106214</v>
@@ -3718,13 +3714,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701431</v>
+        <v>701541</v>
       </c>
       <c r="R28" t="n">
-        <v>6360091</v>
+        <v>6360151</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3785,7 +3781,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308068</v>
+        <v>120308063</v>
       </c>
       <c r="B29" t="n">
         <v>106214</v>
@@ -3825,13 +3821,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701594</v>
+        <v>701532</v>
       </c>
       <c r="R29" t="n">
-        <v>6360147</v>
+        <v>6360141</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3874,7 +3870,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3892,7 +3888,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308053</v>
+        <v>120308066</v>
       </c>
       <c r="B30" t="n">
         <v>106214</v>
@@ -3932,10 +3928,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701497</v>
+        <v>701560</v>
       </c>
       <c r="R30" t="n">
-        <v>6359955</v>
+        <v>6360140</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3970,6 +3966,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3981,7 +3982,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3999,10 +4000,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308066</v>
+        <v>120308042</v>
       </c>
       <c r="B31" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4015,16 +4016,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4039,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701560</v>
+        <v>701451</v>
       </c>
       <c r="R31" t="n">
-        <v>6360140</v>
+        <v>6359994</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4077,11 +4078,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4093,7 +4089,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4111,10 +4107,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308055</v>
+        <v>120308105</v>
       </c>
       <c r="B32" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,16 +4123,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4144,20 +4140,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701519</v>
+        <v>701480</v>
       </c>
       <c r="R32" t="n">
-        <v>6359965</v>
+        <v>6360120</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4200,7 +4205,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4218,10 +4223,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308071</v>
+        <v>120308094</v>
       </c>
       <c r="B33" t="n">
-        <v>106214</v>
+        <v>97905</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4230,38 +4235,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701636</v>
+        <v>701557</v>
       </c>
       <c r="R33" t="n">
-        <v>6360182</v>
+        <v>6360196</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4307,7 +4321,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4325,10 +4339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308110</v>
+        <v>120308086</v>
       </c>
       <c r="B34" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4341,16 +4355,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4365,13 +4379,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701423</v>
+        <v>701557</v>
       </c>
       <c r="R34" t="n">
-        <v>6360088</v>
+        <v>6360196</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4432,7 +4446,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308112</v>
+        <v>120308071</v>
       </c>
       <c r="B35" t="n">
         <v>106214</v>
@@ -4472,10 +4486,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701407</v>
+        <v>701636</v>
       </c>
       <c r="R35" t="n">
-        <v>6360080</v>
+        <v>6360182</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4521,7 +4535,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4539,10 +4553,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308067</v>
+        <v>120308317</v>
       </c>
       <c r="B36" t="n">
-        <v>106214</v>
+        <v>94704</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4551,25 +4565,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4579,13 +4593,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701574</v>
+        <v>701518</v>
       </c>
       <c r="R36" t="n">
-        <v>6360140</v>
+        <v>6360129</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4625,11 +4639,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4646,10 +4655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308086</v>
+        <v>120308078</v>
       </c>
       <c r="B37" t="n">
-        <v>108811</v>
+        <v>103452</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4662,21 +4671,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4686,13 +4695,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701557</v>
+        <v>701622</v>
       </c>
       <c r="R37" t="n">
-        <v>6360196</v>
+        <v>6360225</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4735,7 +4744,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4753,7 +4762,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308060</v>
+        <v>120308106</v>
       </c>
       <c r="B38" t="n">
         <v>106214</v>
@@ -4793,13 +4802,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701526</v>
+        <v>701480</v>
       </c>
       <c r="R38" t="n">
-        <v>6360046</v>
+        <v>6360120</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4842,7 +4851,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4860,7 +4869,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308102</v>
+        <v>120308110</v>
       </c>
       <c r="B39" t="n">
         <v>106214</v>
@@ -4900,13 +4909,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701532</v>
+        <v>701423</v>
       </c>
       <c r="R39" t="n">
-        <v>6360143</v>
+        <v>6360088</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4967,7 +4976,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308043</v>
+        <v>120308109</v>
       </c>
       <c r="B40" t="n">
         <v>106214</v>
@@ -5007,13 +5016,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701451</v>
+        <v>701431</v>
       </c>
       <c r="R40" t="n">
-        <v>6359994</v>
+        <v>6360091</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5056,7 +5065,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5074,7 +5083,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308100</v>
+        <v>120308068</v>
       </c>
       <c r="B41" t="n">
         <v>106214</v>
@@ -5114,13 +5123,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701541</v>
+        <v>701594</v>
       </c>
       <c r="R41" t="n">
-        <v>6360151</v>
+        <v>6360147</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5163,7 +5172,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5181,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308063</v>
+        <v>120308080</v>
       </c>
       <c r="B42" t="n">
         <v>106214</v>
@@ -5221,10 +5230,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701532</v>
+        <v>701606</v>
       </c>
       <c r="R42" t="n">
-        <v>6360141</v>
+        <v>6360224</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5270,7 +5279,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5288,10 +5297,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308094</v>
+        <v>120308067</v>
       </c>
       <c r="B43" t="n">
-        <v>97905</v>
+        <v>106214</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5300,47 +5309,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701557</v>
+        <v>701574</v>
       </c>
       <c r="R43" t="n">
-        <v>6360196</v>
+        <v>6360140</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308055</v>
+        <v>120308105</v>
       </c>
       <c r="B16" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2409,20 +2409,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701519</v>
+        <v>701480</v>
       </c>
       <c r="R16" t="n">
-        <v>6359965</v>
+        <v>6360120</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2465,7 +2474,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2483,10 +2492,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308062</v>
+        <v>120308317</v>
       </c>
       <c r="B17" t="n">
-        <v>106214</v>
+        <v>94704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,25 +2504,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2523,13 +2532,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701524</v>
+        <v>701518</v>
       </c>
       <c r="R17" t="n">
-        <v>6360079</v>
+        <v>6360129</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,11 +2578,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2590,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308048</v>
+        <v>120308106</v>
       </c>
       <c r="B18" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,55 +2606,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701438</v>
+        <v>701480</v>
       </c>
       <c r="R18" t="n">
-        <v>6359991</v>
+        <v>6360120</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2693,7 +2683,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2711,7 +2701,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308107</v>
+        <v>120308063</v>
       </c>
       <c r="B19" t="n">
         <v>106214</v>
@@ -2751,13 +2741,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701452</v>
+        <v>701532</v>
       </c>
       <c r="R19" t="n">
-        <v>6360109</v>
+        <v>6360141</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,7 +2790,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2818,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308060</v>
+        <v>120308094</v>
       </c>
       <c r="B20" t="n">
-        <v>106214</v>
+        <v>97905</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2830,38 +2820,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701526</v>
+        <v>701557</v>
       </c>
       <c r="R20" t="n">
-        <v>6360046</v>
+        <v>6360196</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2907,7 +2906,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2925,10 +2924,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308053</v>
+        <v>120308042</v>
       </c>
       <c r="B21" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,16 +2940,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2965,10 +2964,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701497</v>
+        <v>701451</v>
       </c>
       <c r="R21" t="n">
-        <v>6359955</v>
+        <v>6359994</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3139,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308102</v>
+        <v>120308048</v>
       </c>
       <c r="B23" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3151,41 +3150,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701532</v>
+        <v>701438</v>
       </c>
       <c r="R23" t="n">
-        <v>6360143</v>
+        <v>6359991</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3228,7 +3241,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3246,7 +3259,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308059</v>
+        <v>120308060</v>
       </c>
       <c r="B24" t="n">
         <v>106214</v>
@@ -3286,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701524</v>
+        <v>701526</v>
       </c>
       <c r="R24" t="n">
-        <v>6359992</v>
+        <v>6360046</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3335,7 +3348,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3353,7 +3366,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308052</v>
+        <v>120308059</v>
       </c>
       <c r="B25" t="n">
         <v>106214</v>
@@ -3393,10 +3406,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701467</v>
+        <v>701524</v>
       </c>
       <c r="R25" t="n">
-        <v>6359951</v>
+        <v>6359992</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3442,7 +3455,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3567,7 +3580,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308092</v>
+        <v>120308107</v>
       </c>
       <c r="B27" t="n">
         <v>106214</v>
@@ -3607,13 +3620,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701557</v>
+        <v>701452</v>
       </c>
       <c r="R27" t="n">
-        <v>6360196</v>
+        <v>6360109</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3674,7 +3687,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308100</v>
+        <v>120308071</v>
       </c>
       <c r="B28" t="n">
         <v>106214</v>
@@ -3714,13 +3727,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701541</v>
+        <v>701636</v>
       </c>
       <c r="R28" t="n">
-        <v>6360151</v>
+        <v>6360182</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3763,7 +3776,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3781,7 +3794,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308063</v>
+        <v>120308102</v>
       </c>
       <c r="B29" t="n">
         <v>106214</v>
@@ -3824,10 +3837,10 @@
         <v>701532</v>
       </c>
       <c r="R29" t="n">
-        <v>6360141</v>
+        <v>6360143</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3870,7 +3883,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3888,7 +3901,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308066</v>
+        <v>120308053</v>
       </c>
       <c r="B30" t="n">
         <v>106214</v>
@@ -3928,10 +3941,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701560</v>
+        <v>701497</v>
       </c>
       <c r="R30" t="n">
-        <v>6360140</v>
+        <v>6359955</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3966,11 +3979,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3982,7 +3990,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4000,10 +4008,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308042</v>
+        <v>120308100</v>
       </c>
       <c r="B31" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4016,16 +4024,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4040,13 +4048,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701451</v>
+        <v>701541</v>
       </c>
       <c r="R31" t="n">
-        <v>6359994</v>
+        <v>6360151</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4089,7 +4097,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4107,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308105</v>
+        <v>120308067</v>
       </c>
       <c r="B32" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4123,16 +4131,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4140,29 +4148,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701480</v>
+        <v>701574</v>
       </c>
       <c r="R32" t="n">
-        <v>6360120</v>
+        <v>6360140</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4205,7 +4204,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4223,10 +4222,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308094</v>
+        <v>120308062</v>
       </c>
       <c r="B33" t="n">
-        <v>97905</v>
+        <v>106214</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4235,47 +4234,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701557</v>
+        <v>701524</v>
       </c>
       <c r="R33" t="n">
-        <v>6360196</v>
+        <v>6360079</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4321,7 +4311,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4339,10 +4329,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308086</v>
+        <v>120308068</v>
       </c>
       <c r="B34" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4355,16 +4345,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4379,13 +4369,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701557</v>
+        <v>701594</v>
       </c>
       <c r="R34" t="n">
-        <v>6360196</v>
+        <v>6360147</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4428,7 +4418,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4446,7 +4436,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308071</v>
+        <v>120308109</v>
       </c>
       <c r="B35" t="n">
         <v>106214</v>
@@ -4486,13 +4476,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701636</v>
+        <v>701431</v>
       </c>
       <c r="R35" t="n">
-        <v>6360182</v>
+        <v>6360091</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4535,7 +4525,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4553,10 +4543,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308317</v>
+        <v>120308092</v>
       </c>
       <c r="B36" t="n">
-        <v>94704</v>
+        <v>106214</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,25 +4555,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4593,13 +4583,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701518</v>
+        <v>701557</v>
       </c>
       <c r="R36" t="n">
-        <v>6360129</v>
+        <v>6360196</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4639,6 +4629,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4655,10 +4650,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308078</v>
+        <v>120308066</v>
       </c>
       <c r="B37" t="n">
-        <v>103452</v>
+        <v>106214</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,21 +4666,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4695,10 +4690,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701622</v>
+        <v>701560</v>
       </c>
       <c r="R37" t="n">
-        <v>6360225</v>
+        <v>6360140</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4731,6 +4726,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4762,7 +4762,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308106</v>
+        <v>120308052</v>
       </c>
       <c r="B38" t="n">
         <v>106214</v>
@@ -4802,13 +4802,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701480</v>
+        <v>701467</v>
       </c>
       <c r="R38" t="n">
-        <v>6360120</v>
+        <v>6359951</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308110</v>
+        <v>120308055</v>
       </c>
       <c r="B39" t="n">
         <v>106214</v>
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701423</v>
+        <v>701519</v>
       </c>
       <c r="R39" t="n">
-        <v>6360088</v>
+        <v>6359965</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4976,10 +4976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308109</v>
+        <v>120308086</v>
       </c>
       <c r="B40" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,16 +4992,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5016,13 +5016,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701431</v>
+        <v>701557</v>
       </c>
       <c r="R40" t="n">
-        <v>6360091</v>
+        <v>6360196</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308068</v>
+        <v>120308078</v>
       </c>
       <c r="B41" t="n">
-        <v>106214</v>
+        <v>103452</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5099,21 +5099,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701594</v>
+        <v>701622</v>
       </c>
       <c r="R41" t="n">
-        <v>6360147</v>
+        <v>6360225</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308080</v>
+        <v>120308110</v>
       </c>
       <c r="B42" t="n">
         <v>106214</v>
@@ -5230,13 +5230,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701606</v>
+        <v>701423</v>
       </c>
       <c r="R42" t="n">
-        <v>6360224</v>
+        <v>6360088</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308067</v>
+        <v>120308080</v>
       </c>
       <c r="B43" t="n">
         <v>106214</v>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701574</v>
+        <v>701606</v>
       </c>
       <c r="R43" t="n">
-        <v>6360140</v>
+        <v>6360224</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308048</v>
+        <v>120308060</v>
       </c>
       <c r="B23" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,55 +3150,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701438</v>
+        <v>701526</v>
       </c>
       <c r="R23" t="n">
-        <v>6359991</v>
+        <v>6360046</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3259,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308060</v>
+        <v>120308048</v>
       </c>
       <c r="B24" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3271,41 +3257,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701526</v>
+        <v>701438</v>
       </c>
       <c r="R24" t="n">
-        <v>6360046</v>
+        <v>6359991</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308105</v>
+        <v>120308068</v>
       </c>
       <c r="B16" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2409,26 +2409,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701480</v>
+        <v>701594</v>
       </c>
       <c r="R16" t="n">
-        <v>6360120</v>
+        <v>6360147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,7 +2465,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2492,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308317</v>
+        <v>120308112</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
+        <v>106214</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2504,25 +2495,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2532,13 +2523,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701518</v>
+        <v>701407</v>
       </c>
       <c r="R17" t="n">
-        <v>6360129</v>
+        <v>6360080</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2578,6 +2569,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2594,7 +2590,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308106</v>
+        <v>120308062</v>
       </c>
       <c r="B18" t="n">
         <v>106214</v>
@@ -2634,13 +2630,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701480</v>
+        <v>701524</v>
       </c>
       <c r="R18" t="n">
-        <v>6360120</v>
+        <v>6360079</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2683,7 +2679,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2701,7 +2697,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308063</v>
+        <v>120308052</v>
       </c>
       <c r="B19" t="n">
         <v>106214</v>
@@ -2741,10 +2737,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701532</v>
+        <v>701467</v>
       </c>
       <c r="R19" t="n">
-        <v>6360141</v>
+        <v>6359951</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2808,10 +2804,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308094</v>
+        <v>120308053</v>
       </c>
       <c r="B20" t="n">
-        <v>97905</v>
+        <v>106214</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2820,47 +2816,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701557</v>
+        <v>701497</v>
       </c>
       <c r="R20" t="n">
-        <v>6360196</v>
+        <v>6359955</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2906,7 +2893,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2924,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308042</v>
+        <v>120308078</v>
       </c>
       <c r="B21" t="n">
-        <v>108811</v>
+        <v>103452</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2940,21 +2927,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2964,10 +2951,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701451</v>
+        <v>701622</v>
       </c>
       <c r="R21" t="n">
-        <v>6359994</v>
+        <v>6360225</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3013,7 +3000,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3031,7 +3018,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308043</v>
+        <v>120308059</v>
       </c>
       <c r="B22" t="n">
         <v>106214</v>
@@ -3071,10 +3058,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701451</v>
+        <v>701524</v>
       </c>
       <c r="R22" t="n">
-        <v>6359994</v>
+        <v>6359992</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3120,7 +3107,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3138,10 +3125,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308060</v>
+        <v>120308094</v>
       </c>
       <c r="B23" t="n">
-        <v>106214</v>
+        <v>97905</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,38 +3137,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701526</v>
+        <v>701557</v>
       </c>
       <c r="R23" t="n">
-        <v>6360046</v>
+        <v>6360196</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3227,7 +3223,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3245,10 +3241,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308048</v>
+        <v>120308063</v>
       </c>
       <c r="B24" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,55 +3253,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701438</v>
+        <v>701532</v>
       </c>
       <c r="R24" t="n">
-        <v>6359991</v>
+        <v>6360141</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3366,10 +3348,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308059</v>
+        <v>120308048</v>
       </c>
       <c r="B25" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3378,41 +3360,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701524</v>
+        <v>701438</v>
       </c>
       <c r="R25" t="n">
-        <v>6359992</v>
+        <v>6359991</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3455,7 +3451,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3473,7 +3469,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308112</v>
+        <v>120308106</v>
       </c>
       <c r="B26" t="n">
         <v>106214</v>
@@ -3513,13 +3509,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701407</v>
+        <v>701480</v>
       </c>
       <c r="R26" t="n">
-        <v>6360080</v>
+        <v>6360120</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3580,7 +3576,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308107</v>
+        <v>120308102</v>
       </c>
       <c r="B27" t="n">
         <v>106214</v>
@@ -3620,13 +3616,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701452</v>
+        <v>701532</v>
       </c>
       <c r="R27" t="n">
-        <v>6360109</v>
+        <v>6360143</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3687,7 +3683,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308071</v>
+        <v>120308110</v>
       </c>
       <c r="B28" t="n">
         <v>106214</v>
@@ -3727,13 +3723,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701636</v>
+        <v>701423</v>
       </c>
       <c r="R28" t="n">
-        <v>6360182</v>
+        <v>6360088</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3776,7 +3772,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3794,10 +3790,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308102</v>
+        <v>120308105</v>
       </c>
       <c r="B29" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,16 +3806,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3827,20 +3823,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701532</v>
+        <v>701480</v>
       </c>
       <c r="R29" t="n">
-        <v>6360143</v>
+        <v>6360120</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3901,7 +3906,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308053</v>
+        <v>120308055</v>
       </c>
       <c r="B30" t="n">
         <v>106214</v>
@@ -3941,10 +3946,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701497</v>
+        <v>701519</v>
       </c>
       <c r="R30" t="n">
-        <v>6359955</v>
+        <v>6359965</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4008,7 +4013,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308100</v>
+        <v>120308067</v>
       </c>
       <c r="B31" t="n">
         <v>106214</v>
@@ -4048,13 +4053,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701541</v>
+        <v>701574</v>
       </c>
       <c r="R31" t="n">
-        <v>6360151</v>
+        <v>6360140</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4097,7 +4102,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4115,7 +4120,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308067</v>
+        <v>120308060</v>
       </c>
       <c r="B32" t="n">
         <v>106214</v>
@@ -4155,10 +4160,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701574</v>
+        <v>701526</v>
       </c>
       <c r="R32" t="n">
-        <v>6360140</v>
+        <v>6360046</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4204,7 +4209,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4222,7 +4227,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308062</v>
+        <v>120308066</v>
       </c>
       <c r="B33" t="n">
         <v>106214</v>
@@ -4262,10 +4267,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701524</v>
+        <v>701560</v>
       </c>
       <c r="R33" t="n">
-        <v>6360079</v>
+        <v>6360140</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4300,6 +4305,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4311,7 +4321,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4329,7 +4339,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308068</v>
+        <v>120308071</v>
       </c>
       <c r="B34" t="n">
         <v>106214</v>
@@ -4369,13 +4379,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701594</v>
+        <v>701636</v>
       </c>
       <c r="R34" t="n">
-        <v>6360147</v>
+        <v>6360182</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4446,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308109</v>
+        <v>120308100</v>
       </c>
       <c r="B35" t="n">
         <v>106214</v>
@@ -4476,13 +4486,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701431</v>
+        <v>701541</v>
       </c>
       <c r="R35" t="n">
-        <v>6360091</v>
+        <v>6360151</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4543,7 +4553,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308092</v>
+        <v>120308109</v>
       </c>
       <c r="B36" t="n">
         <v>106214</v>
@@ -4583,13 +4593,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701557</v>
+        <v>701431</v>
       </c>
       <c r="R36" t="n">
-        <v>6360196</v>
+        <v>6360091</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4650,10 +4660,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308066</v>
+        <v>120308086</v>
       </c>
       <c r="B37" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4666,16 +4676,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4690,13 +4700,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701560</v>
+        <v>701557</v>
       </c>
       <c r="R37" t="n">
-        <v>6360140</v>
+        <v>6360196</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4728,11 +4738,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4762,7 +4767,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308052</v>
+        <v>120308043</v>
       </c>
       <c r="B38" t="n">
         <v>106214</v>
@@ -4802,10 +4807,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701467</v>
+        <v>701451</v>
       </c>
       <c r="R38" t="n">
-        <v>6359951</v>
+        <v>6359994</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4869,7 +4874,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308055</v>
+        <v>120308092</v>
       </c>
       <c r="B39" t="n">
         <v>106214</v>
@@ -4909,10 +4914,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701519</v>
+        <v>701557</v>
       </c>
       <c r="R39" t="n">
-        <v>6359965</v>
+        <v>6360196</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4958,7 +4963,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4976,10 +4981,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308086</v>
+        <v>120308317</v>
       </c>
       <c r="B40" t="n">
-        <v>108811</v>
+        <v>94704</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4988,25 +4993,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5016,13 +5021,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701557</v>
+        <v>701518</v>
       </c>
       <c r="R40" t="n">
-        <v>6360196</v>
+        <v>6360129</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5062,11 +5067,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5083,10 +5083,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308078</v>
+        <v>120308080</v>
       </c>
       <c r="B41" t="n">
-        <v>103452</v>
+        <v>106214</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5099,21 +5099,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701622</v>
+        <v>701606</v>
       </c>
       <c r="R41" t="n">
-        <v>6360225</v>
+        <v>6360224</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308110</v>
+        <v>120308042</v>
       </c>
       <c r="B42" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5230,13 +5230,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701423</v>
+        <v>701451</v>
       </c>
       <c r="R42" t="n">
-        <v>6360088</v>
+        <v>6359994</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308080</v>
+        <v>120308107</v>
       </c>
       <c r="B43" t="n">
         <v>106214</v>
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701606</v>
+        <v>701452</v>
       </c>
       <c r="R43" t="n">
-        <v>6360224</v>
+        <v>6360109</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308068</v>
+        <v>120308086</v>
       </c>
       <c r="B16" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2416,13 +2416,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701594</v>
+        <v>701557</v>
       </c>
       <c r="R16" t="n">
-        <v>6360147</v>
+        <v>6360196</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308112</v>
+        <v>120308042</v>
       </c>
       <c r="B17" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2499,16 +2499,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701407</v>
+        <v>701451</v>
       </c>
       <c r="R17" t="n">
-        <v>6360080</v>
+        <v>6359994</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308062</v>
+        <v>120308102</v>
       </c>
       <c r="B18" t="n">
         <v>106214</v>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701524</v>
+        <v>701532</v>
       </c>
       <c r="R18" t="n">
-        <v>6360079</v>
+        <v>6360143</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2697,10 +2697,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308052</v>
+        <v>120308047</v>
       </c>
       <c r="B19" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,41 +2709,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701467</v>
+        <v>701438</v>
       </c>
       <c r="R19" t="n">
-        <v>6359951</v>
+        <v>6359991</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2804,7 +2818,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308053</v>
+        <v>120308100</v>
       </c>
       <c r="B20" t="n">
         <v>106214</v>
@@ -2844,13 +2858,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701497</v>
+        <v>701541</v>
       </c>
       <c r="R20" t="n">
-        <v>6359955</v>
+        <v>6360151</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2893,7 +2907,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2911,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308078</v>
+        <v>120308055</v>
       </c>
       <c r="B21" t="n">
-        <v>103452</v>
+        <v>106214</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2927,21 +2941,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2951,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701622</v>
+        <v>701519</v>
       </c>
       <c r="R21" t="n">
-        <v>6360225</v>
+        <v>6359965</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3000,7 +3014,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3018,7 +3032,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308059</v>
+        <v>120308067</v>
       </c>
       <c r="B22" t="n">
         <v>106214</v>
@@ -3058,10 +3072,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701524</v>
+        <v>701574</v>
       </c>
       <c r="R22" t="n">
-        <v>6359992</v>
+        <v>6360140</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3107,7 +3121,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3125,10 +3139,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308094</v>
+        <v>120308106</v>
       </c>
       <c r="B23" t="n">
-        <v>97905</v>
+        <v>106214</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,50 +3151,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701557</v>
+        <v>701480</v>
       </c>
       <c r="R23" t="n">
-        <v>6360196</v>
+        <v>6360120</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3241,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308063</v>
+        <v>120308107</v>
       </c>
       <c r="B24" t="n">
         <v>106214</v>
@@ -3281,13 +3286,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701532</v>
+        <v>701452</v>
       </c>
       <c r="R24" t="n">
-        <v>6360141</v>
+        <v>6360109</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3330,7 +3335,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3348,10 +3353,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308048</v>
+        <v>120308110</v>
       </c>
       <c r="B25" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3360,55 +3365,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701438</v>
+        <v>701423</v>
       </c>
       <c r="R25" t="n">
-        <v>6359991</v>
+        <v>6360088</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3451,7 +3442,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3469,7 +3460,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308106</v>
+        <v>120308053</v>
       </c>
       <c r="B26" t="n">
         <v>106214</v>
@@ -3509,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701480</v>
+        <v>701497</v>
       </c>
       <c r="R26" t="n">
-        <v>6360120</v>
+        <v>6359955</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3558,7 +3549,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3576,7 +3567,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308102</v>
+        <v>120308080</v>
       </c>
       <c r="B27" t="n">
         <v>106214</v>
@@ -3616,13 +3607,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701532</v>
+        <v>701606</v>
       </c>
       <c r="R27" t="n">
-        <v>6360143</v>
+        <v>6360224</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3665,7 +3656,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3683,7 +3674,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308110</v>
+        <v>120308062</v>
       </c>
       <c r="B28" t="n">
         <v>106214</v>
@@ -3723,13 +3714,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701423</v>
+        <v>701524</v>
       </c>
       <c r="R28" t="n">
-        <v>6360088</v>
+        <v>6360079</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3772,7 +3763,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3790,10 +3781,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308105</v>
+        <v>120308043</v>
       </c>
       <c r="B29" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3806,16 +3797,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3823,29 +3814,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701480</v>
+        <v>701451</v>
       </c>
       <c r="R29" t="n">
-        <v>6360120</v>
+        <v>6359994</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3888,7 +3870,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3906,7 +3888,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308055</v>
+        <v>120308071</v>
       </c>
       <c r="B30" t="n">
         <v>106214</v>
@@ -3946,10 +3928,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701519</v>
+        <v>701636</v>
       </c>
       <c r="R30" t="n">
-        <v>6359965</v>
+        <v>6360182</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3995,7 +3977,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4013,7 +3995,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308067</v>
+        <v>120308052</v>
       </c>
       <c r="B31" t="n">
         <v>106214</v>
@@ -4053,10 +4035,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701574</v>
+        <v>701467</v>
       </c>
       <c r="R31" t="n">
-        <v>6360140</v>
+        <v>6359951</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4102,7 +4084,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4120,7 +4102,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308060</v>
+        <v>120308092</v>
       </c>
       <c r="B32" t="n">
         <v>106214</v>
@@ -4160,10 +4142,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701526</v>
+        <v>701557</v>
       </c>
       <c r="R32" t="n">
-        <v>6360046</v>
+        <v>6360196</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4209,7 +4191,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4227,7 +4209,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308066</v>
+        <v>120308060</v>
       </c>
       <c r="B33" t="n">
         <v>106214</v>
@@ -4267,10 +4249,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701560</v>
+        <v>701526</v>
       </c>
       <c r="R33" t="n">
-        <v>6360140</v>
+        <v>6360046</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4305,11 +4287,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4321,7 +4298,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4339,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308071</v>
+        <v>120308078</v>
       </c>
       <c r="B34" t="n">
-        <v>106214</v>
+        <v>103452</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4355,21 +4332,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4379,10 +4356,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701636</v>
+        <v>701622</v>
       </c>
       <c r="R34" t="n">
-        <v>6360182</v>
+        <v>6360225</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4446,7 +4423,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308100</v>
+        <v>120308059</v>
       </c>
       <c r="B35" t="n">
         <v>106214</v>
@@ -4486,13 +4463,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701541</v>
+        <v>701524</v>
       </c>
       <c r="R35" t="n">
-        <v>6360151</v>
+        <v>6359992</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4535,7 +4512,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4660,7 +4637,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308086</v>
+        <v>120308105</v>
       </c>
       <c r="B37" t="n">
         <v>108811</v>
@@ -4693,20 +4670,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701557</v>
+        <v>701480</v>
       </c>
       <c r="R37" t="n">
-        <v>6360196</v>
+        <v>6360120</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4767,10 +4753,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308043</v>
+        <v>120308094</v>
       </c>
       <c r="B38" t="n">
-        <v>106214</v>
+        <v>97905</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4779,38 +4765,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701451</v>
+        <v>701557</v>
       </c>
       <c r="R38" t="n">
-        <v>6359994</v>
+        <v>6360196</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4856,7 +4851,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4874,7 +4869,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308092</v>
+        <v>120308066</v>
       </c>
       <c r="B39" t="n">
         <v>106214</v>
@@ -4914,10 +4909,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701557</v>
+        <v>701560</v>
       </c>
       <c r="R39" t="n">
-        <v>6360196</v>
+        <v>6360140</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4952,6 +4947,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308080</v>
+        <v>120308063</v>
       </c>
       <c r="B41" t="n">
         <v>106214</v>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701606</v>
+        <v>701532</v>
       </c>
       <c r="R41" t="n">
-        <v>6360224</v>
+        <v>6360141</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308042</v>
+        <v>120308068</v>
       </c>
       <c r="B42" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5230,13 +5230,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701451</v>
+        <v>701594</v>
       </c>
       <c r="R42" t="n">
-        <v>6359994</v>
+        <v>6360147</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308107</v>
+        <v>120308112</v>
       </c>
       <c r="B43" t="n">
         <v>106214</v>
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701452</v>
+        <v>701407</v>
       </c>
       <c r="R43" t="n">
-        <v>6360109</v>
+        <v>6360080</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -4981,10 +4981,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308317</v>
+        <v>120308063</v>
       </c>
       <c r="B40" t="n">
-        <v>94704</v>
+        <v>106214</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4993,25 +4993,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701518</v>
+        <v>701532</v>
       </c>
       <c r="R40" t="n">
-        <v>6360129</v>
+        <v>6360141</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5067,6 +5067,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5083,10 +5088,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308063</v>
+        <v>120308317</v>
       </c>
       <c r="B41" t="n">
-        <v>106214</v>
+        <v>94704</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5095,25 +5100,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5123,13 +5128,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701532</v>
+        <v>701518</v>
       </c>
       <c r="R41" t="n">
-        <v>6360141</v>
+        <v>6360129</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5169,11 +5174,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2376,7 +2376,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308086</v>
+        <v>120308105</v>
       </c>
       <c r="B16" t="n">
         <v>108811</v>
@@ -2409,20 +2409,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701557</v>
+        <v>701480</v>
       </c>
       <c r="R16" t="n">
-        <v>6360196</v>
+        <v>6360120</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2483,10 +2492,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308042</v>
+        <v>120308063</v>
       </c>
       <c r="B17" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2499,16 +2508,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2523,10 +2532,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701451</v>
+        <v>701532</v>
       </c>
       <c r="R17" t="n">
-        <v>6359994</v>
+        <v>6360141</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2590,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308102</v>
+        <v>120308317</v>
       </c>
       <c r="B18" t="n">
-        <v>106214</v>
+        <v>94704</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,25 +2611,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2630,13 +2639,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701532</v>
+        <v>701518</v>
       </c>
       <c r="R18" t="n">
-        <v>6360143</v>
+        <v>6360129</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2676,11 +2685,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2697,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308047</v>
+        <v>120308068</v>
       </c>
       <c r="B19" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,55 +2713,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701438</v>
+        <v>701594</v>
       </c>
       <c r="R19" t="n">
-        <v>6359991</v>
+        <v>6360147</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,7 +2790,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2818,7 +2808,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308100</v>
+        <v>120308071</v>
       </c>
       <c r="B20" t="n">
         <v>106214</v>
@@ -2858,13 +2848,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701541</v>
+        <v>701636</v>
       </c>
       <c r="R20" t="n">
-        <v>6360151</v>
+        <v>6360182</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2907,7 +2897,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2925,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308055</v>
+        <v>120308042</v>
       </c>
       <c r="B21" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,16 +2931,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2965,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701519</v>
+        <v>701451</v>
       </c>
       <c r="R21" t="n">
-        <v>6359965</v>
+        <v>6359994</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3032,7 +3022,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308067</v>
+        <v>120308060</v>
       </c>
       <c r="B22" t="n">
         <v>106214</v>
@@ -3072,10 +3062,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701574</v>
+        <v>701526</v>
       </c>
       <c r="R22" t="n">
-        <v>6360140</v>
+        <v>6360046</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3121,7 +3111,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3139,7 +3129,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308106</v>
+        <v>120308053</v>
       </c>
       <c r="B23" t="n">
         <v>106214</v>
@@ -3179,13 +3169,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701480</v>
+        <v>701497</v>
       </c>
       <c r="R23" t="n">
-        <v>6360120</v>
+        <v>6359955</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3228,7 +3218,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3246,7 +3236,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308107</v>
+        <v>120308067</v>
       </c>
       <c r="B24" t="n">
         <v>106214</v>
@@ -3286,13 +3276,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701452</v>
+        <v>701574</v>
       </c>
       <c r="R24" t="n">
-        <v>6360109</v>
+        <v>6360140</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3335,7 +3325,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3353,7 +3343,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308110</v>
+        <v>120308112</v>
       </c>
       <c r="B25" t="n">
         <v>106214</v>
@@ -3393,13 +3383,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701423</v>
+        <v>701407</v>
       </c>
       <c r="R25" t="n">
-        <v>6360088</v>
+        <v>6360080</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,7 +3450,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308053</v>
+        <v>120308055</v>
       </c>
       <c r="B26" t="n">
         <v>106214</v>
@@ -3500,10 +3490,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701497</v>
+        <v>701519</v>
       </c>
       <c r="R26" t="n">
-        <v>6359955</v>
+        <v>6359965</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3567,7 +3557,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308080</v>
+        <v>120308110</v>
       </c>
       <c r="B27" t="n">
         <v>106214</v>
@@ -3607,13 +3597,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701606</v>
+        <v>701423</v>
       </c>
       <c r="R27" t="n">
-        <v>6360224</v>
+        <v>6360088</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3656,7 +3646,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3674,7 +3664,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308062</v>
+        <v>120308102</v>
       </c>
       <c r="B28" t="n">
         <v>106214</v>
@@ -3714,13 +3704,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701524</v>
+        <v>701532</v>
       </c>
       <c r="R28" t="n">
-        <v>6360079</v>
+        <v>6360143</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3763,7 +3753,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3781,10 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308043</v>
+        <v>120308086</v>
       </c>
       <c r="B29" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3797,16 +3787,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3821,13 +3811,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701451</v>
+        <v>701557</v>
       </c>
       <c r="R29" t="n">
-        <v>6359994</v>
+        <v>6360196</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3870,7 +3860,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3888,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308071</v>
+        <v>120308078</v>
       </c>
       <c r="B30" t="n">
-        <v>106214</v>
+        <v>103452</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3904,21 +3894,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3928,10 +3918,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701636</v>
+        <v>701622</v>
       </c>
       <c r="R30" t="n">
-        <v>6360182</v>
+        <v>6360225</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3995,7 +3985,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308052</v>
+        <v>120308092</v>
       </c>
       <c r="B31" t="n">
         <v>106214</v>
@@ -4035,10 +4025,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701467</v>
+        <v>701557</v>
       </c>
       <c r="R31" t="n">
-        <v>6359951</v>
+        <v>6360196</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4084,7 +4074,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4102,10 +4092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308092</v>
+        <v>120308047</v>
       </c>
       <c r="B32" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4114,41 +4104,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701557</v>
+        <v>701438</v>
       </c>
       <c r="R32" t="n">
-        <v>6360196</v>
+        <v>6359991</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4209,7 +4213,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308060</v>
+        <v>120308100</v>
       </c>
       <c r="B33" t="n">
         <v>106214</v>
@@ -4249,13 +4253,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701526</v>
+        <v>701541</v>
       </c>
       <c r="R33" t="n">
-        <v>6360046</v>
+        <v>6360151</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4298,7 +4302,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4316,10 +4320,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308078</v>
+        <v>120308052</v>
       </c>
       <c r="B34" t="n">
-        <v>103452</v>
+        <v>106214</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,21 +4336,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4356,10 +4360,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701622</v>
+        <v>701467</v>
       </c>
       <c r="R34" t="n">
-        <v>6360225</v>
+        <v>6359951</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4405,7 +4409,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4423,7 +4427,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308059</v>
+        <v>120308109</v>
       </c>
       <c r="B35" t="n">
         <v>106214</v>
@@ -4463,13 +4467,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701524</v>
+        <v>701431</v>
       </c>
       <c r="R35" t="n">
-        <v>6359992</v>
+        <v>6360091</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4512,7 +4516,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4530,7 +4534,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308109</v>
+        <v>120308062</v>
       </c>
       <c r="B36" t="n">
         <v>106214</v>
@@ -4570,13 +4574,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701431</v>
+        <v>701524</v>
       </c>
       <c r="R36" t="n">
-        <v>6360091</v>
+        <v>6360079</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4619,7 +4623,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4637,10 +4641,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308105</v>
+        <v>120308059</v>
       </c>
       <c r="B37" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4653,16 +4657,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4670,29 +4674,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701480</v>
+        <v>701524</v>
       </c>
       <c r="R37" t="n">
-        <v>6360120</v>
+        <v>6359992</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4735,7 +4730,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4753,10 +4748,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308094</v>
+        <v>120308107</v>
       </c>
       <c r="B38" t="n">
-        <v>97905</v>
+        <v>106214</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4765,50 +4760,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701557</v>
+        <v>701452</v>
       </c>
       <c r="R38" t="n">
-        <v>6360196</v>
+        <v>6360109</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4869,7 +4855,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308066</v>
+        <v>120308080</v>
       </c>
       <c r="B39" t="n">
         <v>106214</v>
@@ -4909,10 +4895,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701560</v>
+        <v>701606</v>
       </c>
       <c r="R39" t="n">
-        <v>6360140</v>
+        <v>6360224</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4945,11 +4931,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4981,10 +4962,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308063</v>
+        <v>120308094</v>
       </c>
       <c r="B40" t="n">
-        <v>106214</v>
+        <v>97905</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4993,38 +4974,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701532</v>
+        <v>701557</v>
       </c>
       <c r="R40" t="n">
-        <v>6360141</v>
+        <v>6360196</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5070,7 +5060,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5088,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308317</v>
+        <v>120308106</v>
       </c>
       <c r="B41" t="n">
-        <v>94704</v>
+        <v>106214</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5100,25 +5090,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5128,10 +5118,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701518</v>
+        <v>701480</v>
       </c>
       <c r="R41" t="n">
-        <v>6360129</v>
+        <v>6360120</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5174,6 +5164,11 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5190,7 +5185,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308068</v>
+        <v>120308043</v>
       </c>
       <c r="B42" t="n">
         <v>106214</v>
@@ -5230,13 +5225,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701594</v>
+        <v>701451</v>
       </c>
       <c r="R42" t="n">
-        <v>6360147</v>
+        <v>6359994</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5297,7 +5292,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308112</v>
+        <v>120308066</v>
       </c>
       <c r="B43" t="n">
         <v>106214</v>
@@ -5337,10 +5332,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701407</v>
+        <v>701560</v>
       </c>
       <c r="R43" t="n">
-        <v>6360080</v>
+        <v>6360140</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5375,6 +5370,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308105</v>
+        <v>120308110</v>
       </c>
       <c r="B16" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2409,26 +2409,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701480</v>
+        <v>701423</v>
       </c>
       <c r="R16" t="n">
-        <v>6360120</v>
+        <v>6360088</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2599,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308317</v>
+        <v>120308092</v>
       </c>
       <c r="B18" t="n">
-        <v>94704</v>
+        <v>106214</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,25 +2602,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,13 +2630,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701518</v>
+        <v>701557</v>
       </c>
       <c r="R18" t="n">
-        <v>6360129</v>
+        <v>6360196</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,6 +2676,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2701,10 +2697,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308068</v>
+        <v>120308094</v>
       </c>
       <c r="B19" t="n">
-        <v>106214</v>
+        <v>97905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,41 +2709,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701594</v>
+        <v>701557</v>
       </c>
       <c r="R19" t="n">
-        <v>6360147</v>
+        <v>6360196</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2790,7 +2795,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2808,7 +2813,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308071</v>
+        <v>120308106</v>
       </c>
       <c r="B20" t="n">
         <v>106214</v>
@@ -2848,13 +2853,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701636</v>
+        <v>701480</v>
       </c>
       <c r="R20" t="n">
-        <v>6360182</v>
+        <v>6360120</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2897,7 +2902,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2915,10 +2920,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308042</v>
+        <v>120308107</v>
       </c>
       <c r="B21" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,16 +2936,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2955,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701451</v>
+        <v>701452</v>
       </c>
       <c r="R21" t="n">
-        <v>6359994</v>
+        <v>6360109</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3004,7 +3009,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3022,7 +3027,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308060</v>
+        <v>120308052</v>
       </c>
       <c r="B22" t="n">
         <v>106214</v>
@@ -3062,10 +3067,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701526</v>
+        <v>701467</v>
       </c>
       <c r="R22" t="n">
-        <v>6360046</v>
+        <v>6359951</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3129,7 +3134,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308053</v>
+        <v>120308055</v>
       </c>
       <c r="B23" t="n">
         <v>106214</v>
@@ -3169,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701497</v>
+        <v>701519</v>
       </c>
       <c r="R23" t="n">
-        <v>6359955</v>
+        <v>6359965</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3236,10 +3241,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308067</v>
+        <v>120308042</v>
       </c>
       <c r="B24" t="n">
-        <v>106214</v>
+        <v>108811</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3252,16 +3257,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3276,10 +3281,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701574</v>
+        <v>701451</v>
       </c>
       <c r="R24" t="n">
-        <v>6360140</v>
+        <v>6359994</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3325,7 +3330,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3343,7 +3348,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308112</v>
+        <v>120308059</v>
       </c>
       <c r="B25" t="n">
         <v>106214</v>
@@ -3383,10 +3388,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701407</v>
+        <v>701524</v>
       </c>
       <c r="R25" t="n">
-        <v>6360080</v>
+        <v>6359992</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3432,7 +3437,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3450,7 +3455,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308055</v>
+        <v>120308043</v>
       </c>
       <c r="B26" t="n">
         <v>106214</v>
@@ -3490,10 +3495,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701519</v>
+        <v>701451</v>
       </c>
       <c r="R26" t="n">
-        <v>6359965</v>
+        <v>6359994</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3557,7 +3562,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308110</v>
+        <v>120308080</v>
       </c>
       <c r="B27" t="n">
         <v>106214</v>
@@ -3597,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701423</v>
+        <v>701606</v>
       </c>
       <c r="R27" t="n">
-        <v>6360088</v>
+        <v>6360224</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3646,7 +3651,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3664,7 +3669,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308102</v>
+        <v>120308109</v>
       </c>
       <c r="B28" t="n">
         <v>106214</v>
@@ -3704,13 +3709,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701532</v>
+        <v>701431</v>
       </c>
       <c r="R28" t="n">
-        <v>6360143</v>
+        <v>6360091</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3771,10 +3776,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308086</v>
+        <v>120308071</v>
       </c>
       <c r="B29" t="n">
-        <v>108811</v>
+        <v>106214</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3787,16 +3792,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3811,13 +3816,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701557</v>
+        <v>701636</v>
       </c>
       <c r="R29" t="n">
-        <v>6360196</v>
+        <v>6360182</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3860,7 +3865,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3878,10 +3883,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308078</v>
+        <v>120308086</v>
       </c>
       <c r="B30" t="n">
-        <v>103452</v>
+        <v>108811</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,21 +3899,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3918,13 +3923,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701622</v>
+        <v>701557</v>
       </c>
       <c r="R30" t="n">
-        <v>6360225</v>
+        <v>6360196</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3967,7 +3972,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3985,7 +3990,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308092</v>
+        <v>120308053</v>
       </c>
       <c r="B31" t="n">
         <v>106214</v>
@@ -4025,10 +4030,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701557</v>
+        <v>701497</v>
       </c>
       <c r="R31" t="n">
-        <v>6360196</v>
+        <v>6359955</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +4079,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4092,10 +4097,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308047</v>
+        <v>120308067</v>
       </c>
       <c r="B32" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4104,55 +4109,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701438</v>
+        <v>701574</v>
       </c>
       <c r="R32" t="n">
-        <v>6359991</v>
+        <v>6360140</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4195,7 +4186,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4213,7 +4204,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308100</v>
+        <v>120308112</v>
       </c>
       <c r="B33" t="n">
         <v>106214</v>
@@ -4253,13 +4244,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701541</v>
+        <v>701407</v>
       </c>
       <c r="R33" t="n">
-        <v>6360151</v>
+        <v>6360080</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4320,10 +4311,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308052</v>
+        <v>120308047</v>
       </c>
       <c r="B34" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,41 +4323,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701467</v>
+        <v>701438</v>
       </c>
       <c r="R34" t="n">
-        <v>6359951</v>
+        <v>6359991</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4427,7 +4432,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308109</v>
+        <v>120308060</v>
       </c>
       <c r="B35" t="n">
         <v>106214</v>
@@ -4467,13 +4472,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701431</v>
+        <v>701526</v>
       </c>
       <c r="R35" t="n">
-        <v>6360091</v>
+        <v>6360046</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4516,7 +4521,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4534,7 +4539,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308062</v>
+        <v>120308066</v>
       </c>
       <c r="B36" t="n">
         <v>106214</v>
@@ -4574,10 +4579,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701524</v>
+        <v>701560</v>
       </c>
       <c r="R36" t="n">
-        <v>6360079</v>
+        <v>6360140</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4612,6 +4617,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4623,7 +4633,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4641,10 +4651,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308059</v>
+        <v>120308078</v>
       </c>
       <c r="B37" t="n">
-        <v>106214</v>
+        <v>103452</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4657,21 +4667,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4681,10 +4691,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701524</v>
+        <v>701622</v>
       </c>
       <c r="R37" t="n">
-        <v>6359992</v>
+        <v>6360225</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4730,7 +4740,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4748,7 +4758,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308107</v>
+        <v>120308068</v>
       </c>
       <c r="B38" t="n">
         <v>106214</v>
@@ -4788,10 +4798,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701452</v>
+        <v>701594</v>
       </c>
       <c r="R38" t="n">
-        <v>6360109</v>
+        <v>6360147</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4837,7 +4847,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4855,7 +4865,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308080</v>
+        <v>120308100</v>
       </c>
       <c r="B39" t="n">
         <v>106214</v>
@@ -4895,13 +4905,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701606</v>
+        <v>701541</v>
       </c>
       <c r="R39" t="n">
-        <v>6360224</v>
+        <v>6360151</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4944,7 +4954,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4962,10 +4972,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308094</v>
+        <v>120308105</v>
       </c>
       <c r="B40" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4974,30 +4984,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5011,13 +5021,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701557</v>
+        <v>701480</v>
       </c>
       <c r="R40" t="n">
-        <v>6360196</v>
+        <v>6360120</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5078,10 +5088,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308106</v>
+        <v>120308317</v>
       </c>
       <c r="B41" t="n">
-        <v>106214</v>
+        <v>94704</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,25 +5100,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5118,10 +5128,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701480</v>
+        <v>701518</v>
       </c>
       <c r="R41" t="n">
-        <v>6360120</v>
+        <v>6360129</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5164,11 +5174,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5185,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308043</v>
+        <v>120308062</v>
       </c>
       <c r="B42" t="n">
         <v>106214</v>
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701451</v>
+        <v>701524</v>
       </c>
       <c r="R42" t="n">
-        <v>6359994</v>
+        <v>6360079</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5292,7 +5297,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308066</v>
+        <v>120308102</v>
       </c>
       <c r="B43" t="n">
         <v>106214</v>
@@ -5332,13 +5337,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701560</v>
+        <v>701532</v>
       </c>
       <c r="R43" t="n">
-        <v>6360140</v>
+        <v>6360143</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5370,11 +5375,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -4311,10 +4311,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308047</v>
+        <v>120308060</v>
       </c>
       <c r="B34" t="n">
-        <v>108572</v>
+        <v>106214</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4323,55 +4323,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701438</v>
+        <v>701526</v>
       </c>
       <c r="R34" t="n">
-        <v>6359991</v>
+        <v>6360046</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4432,10 +4418,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308060</v>
+        <v>120308047</v>
       </c>
       <c r="B35" t="n">
-        <v>106214</v>
+        <v>108572</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4444,41 +4430,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701526</v>
+        <v>701438</v>
       </c>
       <c r="R35" t="n">
-        <v>6360046</v>
+        <v>6359991</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308317</v>
+        <v>120308062</v>
       </c>
       <c r="B41" t="n">
-        <v>94704</v>
+        <v>106214</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5100,25 +5100,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701518</v>
+        <v>701524</v>
       </c>
       <c r="R41" t="n">
-        <v>6360129</v>
+        <v>6360079</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5174,6 +5174,11 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5190,10 +5195,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308062</v>
+        <v>120308317</v>
       </c>
       <c r="B42" t="n">
-        <v>106214</v>
+        <v>94704</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5202,25 +5207,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5230,13 +5235,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701524</v>
+        <v>701518</v>
       </c>
       <c r="R42" t="n">
-        <v>6360079</v>
+        <v>6360129</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5276,11 +5281,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -3360,7 +3360,7 @@
         <v>120308048</v>
       </c>
       <c r="B25" t="n">
-        <v>108647</v>
+        <v>108750</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>69178536</v>
       </c>
       <c r="B2" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701530.9328588676</v>
+        <v>701531</v>
       </c>
       <c r="R2" t="n">
-        <v>6360077.749022003</v>
+        <v>6360078</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2017-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69178532</v>
+        <v>89807762</v>
       </c>
       <c r="B3" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4405</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,22 +816,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701530.9328588676</v>
+        <v>701529</v>
       </c>
       <c r="R3" t="n">
-        <v>6360077.749022003</v>
+        <v>6359968</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,55 +871,51 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69178541</v>
+        <v>69178533</v>
       </c>
       <c r="B4" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701530.9328588676</v>
+        <v>701531</v>
       </c>
       <c r="R4" t="n">
-        <v>6360077.749022003</v>
+        <v>6360078</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -999,19 +967,9 @@
           <t>2017-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69178540</v>
+        <v>69178538</v>
       </c>
       <c r="B5" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1988</v>
+        <v>473</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1087,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701530.9328588676</v>
+        <v>701531</v>
       </c>
       <c r="R5" t="n">
-        <v>6360077.749022003</v>
+        <v>6360078</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1120,19 +1073,9 @@
           <t>2017-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,62 +1102,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69178538</v>
+        <v>120308047</v>
       </c>
       <c r="B6" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>473</v>
+        <v>1489</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(Neuman) B. Nord.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701530.9328588676</v>
+        <v>701438</v>
       </c>
       <c r="R6" t="n">
-        <v>6360077.749022003</v>
+        <v>6359991</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,22 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,53 +1197,53 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69178533</v>
+        <v>69178540</v>
       </c>
       <c r="B7" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>449</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1329,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701530.9328588676</v>
+        <v>701531</v>
       </c>
       <c r="R7" t="n">
-        <v>6360077.749022003</v>
+        <v>6360078</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1362,19 +1295,9 @@
           <t>2017-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,15 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69178539</v>
+        <v>120308317</v>
       </c>
       <c r="B8" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,46 +1335,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701530.9328588676</v>
+        <v>701518</v>
       </c>
       <c r="R8" t="n">
-        <v>6360077.749022003</v>
+        <v>6360129</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,22 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,27 +1409,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69178534</v>
+        <v>97356366</v>
       </c>
       <c r="B9" t="n">
-        <v>88845</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,46 +1432,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4188</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701530.9328588676</v>
+        <v>701611</v>
       </c>
       <c r="R9" t="n">
-        <v>6360077.749022003</v>
+        <v>6359962</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,22 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,33 +1503,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69178537</v>
+        <v>69178539</v>
       </c>
       <c r="B10" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1692,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701530.9328588676</v>
+        <v>701531</v>
       </c>
       <c r="R10" t="n">
-        <v>6360077.749022003</v>
+        <v>6360078</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1725,19 +1599,9 @@
           <t>2017-10-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-10-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,37 +1628,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89807762</v>
+        <v>69178537</v>
       </c>
       <c r="B11" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1804,24 +1663,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linde Rangsarve, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701528.7607870691</v>
+        <v>701531</v>
       </c>
       <c r="R11" t="n">
-        <v>6359967.898576742</v>
+        <v>6360078</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1845,22 +1702,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,34 +1716,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89807794</v>
+        <v>69178534</v>
       </c>
       <c r="B12" t="n">
-        <v>88845</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,29 +1764,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linde Rangsarve, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701578.7401091076</v>
+        <v>701531</v>
       </c>
       <c r="R12" t="n">
-        <v>6359964.954672986</v>
+        <v>6360078</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1969,22 +1808,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1993,34 +1822,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89807817</v>
+        <v>89807741</v>
       </c>
       <c r="B13" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,21 +1851,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4188</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2052,7 +1875,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2063,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701486.0434882372</v>
+        <v>701576</v>
       </c>
       <c r="R13" t="n">
-        <v>6359900.379652943</v>
+        <v>6359964</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2096,19 +1919,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,15 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89807741</v>
+        <v>89807794</v>
       </c>
       <c r="B14" t="n">
-        <v>88845</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,12 +1979,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2187,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701576.0648522073</v>
+        <v>701579</v>
       </c>
       <c r="R14" t="n">
-        <v>6359964.282243347</v>
+        <v>6359965</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2220,19 +2028,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2260,15 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97356366</v>
+        <v>69178532</v>
       </c>
       <c r="B15" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,40 +2069,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3215</v>
+        <v>4405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701610.8343016773</v>
+        <v>701531</v>
       </c>
       <c r="R15" t="n">
-        <v>6359962.211193668</v>
+        <v>6360078</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2333,22 +2132,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,72 +2146,77 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308100</v>
+        <v>89807817</v>
       </c>
       <c r="B16" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>6031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701541</v>
+        <v>701486</v>
       </c>
       <c r="R16" t="n">
-        <v>6360151</v>
+        <v>6359900</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2446,12 +2240,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,38 +2254,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308071</v>
+        <v>13185284</v>
       </c>
       <c r="B17" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,37 +2284,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701636</v>
+        <v>701342</v>
       </c>
       <c r="R17" t="n">
-        <v>6360182</v>
+        <v>6360057</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,17 +2342,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2006-06-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2006-06-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,36 +2363,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308092</v>
+        <v>68588838</v>
       </c>
       <c r="B18" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,34 +2390,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701557</v>
+        <v>701415</v>
       </c>
       <c r="R18" t="n">
-        <v>6360196</v>
+        <v>6359952</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2655,17 +2456,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,80 +2477,82 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308094</v>
+        <v>68588850</v>
       </c>
       <c r="B19" t="n">
-        <v>97980</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219797</v>
+        <v>101242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701557</v>
+        <v>701382</v>
       </c>
       <c r="R19" t="n">
-        <v>6360196</v>
+        <v>6360003</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2771,17 +2574,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2792,36 +2595,30 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308042</v>
+        <v>68588873</v>
       </c>
       <c r="B20" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,34 +2626,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701451</v>
+        <v>701378</v>
       </c>
       <c r="R20" t="n">
-        <v>6359994</v>
+        <v>6360008</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2878,17 +2692,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,36 +2713,30 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308105</v>
+        <v>73899486</v>
       </c>
       <c r="B21" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,46 +2744,54 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701480</v>
+        <v>701392</v>
       </c>
       <c r="R21" t="n">
-        <v>6360120</v>
+        <v>6359989</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,17 +2810,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,38 +2829,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308043</v>
+        <v>73899493</v>
       </c>
       <c r="B22" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,34 +2863,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701451</v>
+        <v>701372</v>
       </c>
       <c r="R22" t="n">
-        <v>6359994</v>
+        <v>6360022</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3101,17 +2929,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,38 +2948,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308055</v>
+        <v>73899494</v>
       </c>
       <c r="B23" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,34 +2982,51 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701519</v>
+        <v>701365</v>
       </c>
       <c r="R23" t="n">
-        <v>6359965</v>
+        <v>6360025</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3208,17 +3048,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,38 +3067,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308080</v>
+        <v>73899497</v>
       </c>
       <c r="B24" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,34 +3101,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701606</v>
+        <v>701336</v>
       </c>
       <c r="R24" t="n">
-        <v>6360224</v>
+        <v>6360054</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3315,17 +3167,17 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,90 +3186,88 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308048</v>
+        <v>80433370</v>
       </c>
       <c r="B25" t="n">
-        <v>108776</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1489</v>
+        <v>101242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701438</v>
+        <v>701390</v>
       </c>
       <c r="R25" t="n">
-        <v>6359991</v>
+        <v>6360006</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3436,17 +3286,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3455,38 +3305,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308110</v>
+        <v>80433374</v>
       </c>
       <c r="B26" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,37 +3339,54 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701423</v>
+        <v>701343</v>
       </c>
       <c r="R26" t="n">
-        <v>6360088</v>
+        <v>6360056</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3543,17 +3405,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,76 +3424,84 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308317</v>
+        <v>88866504</v>
       </c>
       <c r="B27" t="n">
-        <v>94779</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>101242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701518</v>
+        <v>701368</v>
       </c>
       <c r="R27" t="n">
-        <v>6360129</v>
+        <v>6360019</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3650,17 +3520,17 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,33 +3539,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308066</v>
+        <v>95822713</v>
       </c>
       <c r="B28" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,34 +3573,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701560</v>
+        <v>701325</v>
       </c>
       <c r="R28" t="n">
-        <v>6360140</v>
+        <v>6360075</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3752,22 +3635,17 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,38 +3654,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308068</v>
+        <v>111836843</v>
       </c>
       <c r="B29" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3815,37 +3688,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701594</v>
+        <v>701392</v>
       </c>
       <c r="R29" t="n">
-        <v>6360147</v>
+        <v>6359993</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3864,17 +3750,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3883,38 +3769,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308112</v>
+        <v>111836851</v>
       </c>
       <c r="B30" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3922,34 +3803,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701407</v>
+        <v>701368</v>
       </c>
       <c r="R30" t="n">
-        <v>6360080</v>
+        <v>6360029</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3971,17 +3865,17 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,38 +3884,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120308062</v>
+        <v>118077428</v>
       </c>
       <c r="B31" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4029,34 +3918,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701524</v>
+        <v>701334</v>
       </c>
       <c r="R31" t="n">
-        <v>6360079</v>
+        <v>6360070</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4078,17 +3980,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,38 +3999,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308109</v>
+        <v>126992416</v>
       </c>
       <c r="B32" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4136,37 +4033,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701431</v>
+        <v>701441</v>
       </c>
       <c r="R32" t="n">
-        <v>6360091</v>
+        <v>6359878</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4185,17 +4095,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,38 +4114,33 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308078</v>
+        <v>126992433</v>
       </c>
       <c r="B33" t="n">
-        <v>103527</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4243,37 +4148,50 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701622</v>
+        <v>701364</v>
       </c>
       <c r="R33" t="n">
-        <v>6360225</v>
+        <v>6360029</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4292,17 +4210,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4311,38 +4229,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308107</v>
+        <v>126992447</v>
       </c>
       <c r="B34" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4350,37 +4263,50 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701452</v>
+        <v>701335</v>
       </c>
       <c r="R34" t="n">
-        <v>6360109</v>
+        <v>6360059</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4399,17 +4325,17 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,73 +4344,87 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308067</v>
+        <v>129317243</v>
       </c>
       <c r="B35" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43299</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221849</v>
+        <v>101260</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701574</v>
+        <v>701618</v>
       </c>
       <c r="R35" t="n">
-        <v>6360140</v>
+        <v>6359923</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4511,12 +4451,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,7 +4470,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Grustag med rikt av backtimjan.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4541,57 +4481,61 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308059</v>
+        <v>120308094</v>
       </c>
       <c r="B36" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701524</v>
+        <v>701557</v>
       </c>
       <c r="R36" t="n">
-        <v>6359992</v>
+        <v>6360196</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4637,7 +4581,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4655,15 +4599,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308060</v>
+        <v>120308078</v>
       </c>
       <c r="B37" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,21 +4610,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4695,10 +4634,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701526</v>
+        <v>701622</v>
       </c>
       <c r="R37" t="n">
-        <v>6360046</v>
+        <v>6360225</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4744,7 +4683,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4762,15 +4701,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308063</v>
+        <v>120308121</v>
       </c>
       <c r="B38" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,21 +4712,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4802,13 +4736,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701532</v>
+        <v>701398</v>
       </c>
       <c r="R38" t="n">
-        <v>6360141</v>
+        <v>6360004</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4851,7 +4785,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog mot körvägkant..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4869,15 +4803,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308052</v>
+        <v>120308124</v>
       </c>
       <c r="B39" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4885,16 +4814,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4902,20 +4831,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701467</v>
+        <v>701398</v>
       </c>
       <c r="R39" t="n">
-        <v>6359951</v>
+        <v>6360004</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4958,7 +4896,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog mot körvägkant..</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4976,15 +4914,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308102</v>
+        <v>120308042</v>
       </c>
       <c r="B40" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,16 +4925,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5016,13 +4949,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701532</v>
+        <v>701451</v>
       </c>
       <c r="R40" t="n">
-        <v>6360143</v>
+        <v>6359994</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5065,7 +4998,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5083,15 +5016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308106</v>
+        <v>120308086</v>
       </c>
       <c r="B41" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5099,16 +5027,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5123,13 +5051,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701480</v>
+        <v>701557</v>
       </c>
       <c r="R41" t="n">
-        <v>6360120</v>
+        <v>6360196</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5190,15 +5118,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308053</v>
+        <v>120308105</v>
       </c>
       <c r="B42" t="n">
-        <v>106289</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5206,16 +5129,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5223,20 +5146,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701497</v>
+        <v>701480</v>
       </c>
       <c r="R42" t="n">
-        <v>6359955</v>
+        <v>6360120</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5279,7 +5211,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5297,15 +5229,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308086</v>
+        <v>120308043</v>
       </c>
       <c r="B43" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5313,16 +5240,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5337,13 +5264,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701557</v>
+        <v>701451</v>
       </c>
       <c r="R43" t="n">
-        <v>6360196</v>
+        <v>6359994</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5386,7 +5313,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5401,6 +5328,2681 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120308052</v>
+      </c>
+      <c r="B44" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>701467</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6359951</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120308053</v>
+      </c>
+      <c r="B45" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>701497</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6359955</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120308055</v>
+      </c>
+      <c r="B46" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>701519</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6359965</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120308059</v>
+      </c>
+      <c r="B47" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>701524</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6359992</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120308060</v>
+      </c>
+      <c r="B48" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>701526</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6360046</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120308062</v>
+      </c>
+      <c r="B49" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>701524</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6360079</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120308063</v>
+      </c>
+      <c r="B50" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>701532</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6360141</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120308066</v>
+      </c>
+      <c r="B51" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>701560</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6360140</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120308067</v>
+      </c>
+      <c r="B52" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>701574</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6360140</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120308068</v>
+      </c>
+      <c r="B53" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>701594</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6360147</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120308071</v>
+      </c>
+      <c r="B54" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>701636</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6360182</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120308076</v>
+      </c>
+      <c r="B55" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>701638</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6360226</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta i gränsgata.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120308080</v>
+      </c>
+      <c r="B56" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>701606</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6360224</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120308092</v>
+      </c>
+      <c r="B57" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>701557</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6360196</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120308100</v>
+      </c>
+      <c r="B58" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>701541</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6360151</v>
+      </c>
+      <c r="S58" t="n">
+        <v>7</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120308102</v>
+      </c>
+      <c r="B59" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>701532</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6360143</v>
+      </c>
+      <c r="S59" t="n">
+        <v>8</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120308106</v>
+      </c>
+      <c r="B60" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>701480</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6360120</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120308107</v>
+      </c>
+      <c r="B61" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>701452</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6360109</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120308109</v>
+      </c>
+      <c r="B62" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>701431</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6360091</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120308110</v>
+      </c>
+      <c r="B63" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>701423</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6360088</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120308112</v>
+      </c>
+      <c r="B64" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>701407</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6360080</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120308122</v>
+      </c>
+      <c r="B65" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>701398</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6360004</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog mot körvägkant..</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129317272</v>
+      </c>
+      <c r="B66" t="n">
+        <v>107516</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>701618</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6359923</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Grustag.</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>89823813</v>
+      </c>
+      <c r="B67" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>701391</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6359996</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2020-11-07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2020-11-07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ingrid Angelöf</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>69178541</v>
+      </c>
+      <c r="B68" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lojsta hed, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>701531</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6360078</v>
+      </c>
+      <c r="S68" t="n">
+        <v>50</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2017-10-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2017-10-15</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>89804386</v>
+      </c>
+      <c r="B69" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>701357</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6360028</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ingrid Angelöf</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178536</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89807762</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178533</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178538</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308047</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178540</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308317</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356366</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178539</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178537</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178534</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89807741</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2055,6 +2120,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89807794</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2161,6 +2231,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178532</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2270,6 +2345,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89807817</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2376,6 +2456,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13185284</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2494,6 +2579,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68588838</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2612,6 +2702,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68588850</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2730,6 +2825,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68588873</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2849,6 +2949,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73899486</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2968,6 +3073,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73899493</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3087,6 +3197,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73899494</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3206,6 +3321,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73899497</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3325,6 +3445,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80433370</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3444,6 +3569,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80433374</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3559,6 +3689,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866504</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3674,6 +3809,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95822713</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3789,6 +3929,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836843</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3904,6 +4049,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836851</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4019,6 +4169,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118077428</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4134,6 +4289,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126992416</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4249,6 +4409,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126992433</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4364,6 +4529,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126992447</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4485,6 +4655,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317243</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4596,6 +4771,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308094</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4698,6 +4878,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308078</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4800,6 +4985,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308121</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4911,6 +5101,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308124</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5013,6 +5208,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308042</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5115,6 +5315,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308086</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5226,6 +5431,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308105</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5328,6 +5538,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308043</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5430,6 +5645,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308052</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5532,6 +5752,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308053</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5634,6 +5859,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308055</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5736,6 +5966,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308059</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5838,6 +6073,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308060</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5940,6 +6180,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308062</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6042,6 +6287,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308063</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6149,6 +6399,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308066</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6251,6 +6506,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308067</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6353,6 +6613,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308068</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6455,6 +6720,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308071</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6557,6 +6827,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308076</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6659,6 +6934,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308080</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6761,6 +7041,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308092</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6863,6 +7148,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308100</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6965,6 +7255,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308102</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7067,6 +7362,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308106</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7169,6 +7469,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308107</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7271,6 +7576,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308109</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7373,6 +7683,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308110</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7475,6 +7790,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308112</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7577,6 +7897,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308122</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7679,6 +8004,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317272</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7788,6 +8118,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89823813</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7894,6 +8229,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69178541</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8003,8 +8343,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89804386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>